--- a/education_forms/024_medical_academy_admission_form--education_forms.xlsx
+++ b/education_forms/024_medical_academy_admission_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>Form Header</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>student_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Student Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date of birth</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>medical_specialty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date of birth</t>
+          <t>Medical Specialty</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_specialty</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical specialty</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_specialty</t>
+          <t>specialty_preference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>medical specialty</t>
+          <t>Preferred Specialty</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical history</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>consent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>medical history</t>
+          <t>Consent</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,62 +750,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>medical history</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -825,7 +779,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -918,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_specialty_choices</t>
+          <t>specialty_preference_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +889,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_specialty_choices</t>
+          <t>specialty_preference_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +906,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medical_specialty_choices</t>
+          <t>specialty_preference_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +923,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medical_specialty_choices</t>
+          <t>specialty_preference_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
